--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129404609</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129404610</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129404604</v>
       </c>
       <c r="B4" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129404607</v>
       </c>
       <c r="B5" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129404608</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129404604</v>
       </c>
       <c r="B2" t="n">
-        <v>91897</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129404594</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ärtriksklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>587155</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7019104</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49189-2025 artfynd.xlsx
+++ b/artfynd/A 49189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129404604</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129404594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>